--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136795141</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136795141</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136795141</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136795141</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136795141</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136795141</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136795132</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136794936</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136795091</v>
       </c>
       <c r="B6" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136795141</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136795132</v>
       </c>
       <c r="B4" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136794936</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136795091</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -931,11 +931,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1046,11 +1042,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136795141</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136795132</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136794936</v>
       </c>
       <c r="B5" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136795091</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136795141</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136795132</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136794936</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136795091</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32782-2026 artfynd.xlsx
+++ b/artfynd/A 32782-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136795075</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136795141</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136795132</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136794936</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>136795091</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
